--- a/inst/extdata/mapping-fruits.xlsx
+++ b/inst/extdata/mapping-fruits.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="79">
   <si>
     <t xml:space="preserve">var</t>
   </si>
@@ -154,13 +154,16 @@
     <t xml:space="preserve">Selected</t>
   </si>
   <si>
-    <t xml:space="preserve">Likes apples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likes bananas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likes oranges</t>
+    <t xml:space="preserve">Likes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bananas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oranges</t>
   </si>
   <si>
     <t xml:space="preserve">1 = It's not bad</t>
@@ -232,25 +235,7 @@
     <t xml:space="preserve">n_fruits == 1 &amp; q2_{1 2 3 97} == 1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">q4 = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">{1 2 3 97}</t>
-    </r>
+    <t xml:space="preserve">q4 = {1 2 3 97}</t>
   </si>
   <si>
     <t xml:space="preserve">#REC</t>
@@ -284,7 +269,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,19 +300,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -364,20 +349,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -574,157 +563,157 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -748,448 +737,448 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>38</v>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>38</v>
+      <c r="E8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="0" t="s">
-        <v>38</v>
+      <c r="E10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>46</v>
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="0" t="n">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C20" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="0" t="n">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="0" t="n">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="0" t="n">
+      <c r="C32" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="0" t="n">
+      <c r="C34" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="C35" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="B36" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <v>97</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1229,152 +1218,155 @@
   </sheetPr>
   <dimension ref="A4:E17"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.66"/>
+  </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>73</v>
+      <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>74</v>
+      <c r="E16" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="0" t="n">
+      <c r="A17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>77</v>
+      <c r="E17" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/mapping-fruits.xlsx
+++ b/inst/extdata/mapping-fruits.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="78">
   <si>
     <t xml:space="preserve">var</t>
   </si>
@@ -193,9 +193,30 @@
     <t xml:space="preserve">Others</t>
   </si>
   <si>
+    <t xml:space="preserve">#COMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_fruits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">((dat_mod |&gt; dplyr::select(q2_1:q2_97)) == 1) |&gt; rowSums()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#IF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_fruits == 0 &amp; q1 == 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q2_99 = 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">#VARL</t>
   </si>
   <si>
+    <t xml:space="preserve">q2_99</t>
+  </si>
+  <si>
     <t xml:space="preserve">q{2 3}_1</t>
   </si>
   <si>
@@ -208,30 +229,6 @@
     <t xml:space="preserve">q{2 3}_97</t>
   </si>
   <si>
-    <t xml:space="preserve">#COMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_fruits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">((dat_mod |&gt; dplyr::select(q2_1:q2_97)) == 1) |&gt; rowSums()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#IF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_fruits == 0 &amp; q1 == 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q2_00 = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q2_00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None selected</t>
-  </si>
-  <si>
     <t xml:space="preserve">n_fruits == 1 &amp; q2_{1 2 3 97} == 1</t>
   </si>
   <si>
@@ -247,10 +244,10 @@
     <t xml:space="preserve">Fruit number category</t>
   </si>
   <si>
-    <t xml:space="preserve">2 or less</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 or 4</t>
+    <t xml:space="preserve">3 or less</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 or 5</t>
   </si>
   <si>
     <t xml:space="preserve">.</t>
@@ -259,7 +256,7 @@
     <t xml:space="preserve">Inf</t>
   </si>
   <si>
-    <t xml:space="preserve">5 and more</t>
+    <t xml:space="preserve">6 and more</t>
   </si>
 </sst>
 </file>
@@ -349,7 +346,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -362,12 +359,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1216,157 +1217,159 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A4:E17"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A3:E17"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="30.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="3" width="8.59"/>
   </cols>
   <sheetData>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="1" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1" t="n">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
